--- a/Documents/Product Catalog/Office/Multipurpose Shelf Specifications.xlsx
+++ b/Documents/Product Catalog/Office/Multipurpose Shelf Specifications.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Product Price List\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Talukder Furniture\Documents\Product Catalog\Office\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61808A97-69BB-4EBE-8054-CDD9BD1A52F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Multipurpose Shelf" sheetId="7" r:id="rId1"/>
@@ -31,7 +32,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Sofa '!$B$1:$R$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Visitor Chair '!$B$1:$R$21</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,6 +41,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -3656,7 +3659,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13">
     <font>
       <sz val="10"/>
@@ -4040,44 +4043,26 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="9" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4097,29 +4082,47 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4158,7 +4161,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4208,7 +4211,7 @@
         <xdr:cNvPr id="46" name="image45.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000081010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4258,7 +4261,7 @@
         <xdr:cNvPr id="47" name="image46.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000082010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4308,7 +4311,7 @@
         <xdr:cNvPr id="52" name="image51.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000087010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000034000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4358,7 +4361,7 @@
         <xdr:cNvPr id="53" name="image52.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000088010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000035000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4413,7 +4416,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4463,7 +4466,7 @@
         <xdr:cNvPr id="54" name="image53.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000089010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000036000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4513,7 +4516,7 @@
         <xdr:cNvPr id="55" name="image54.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008A010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000037000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4563,7 +4566,7 @@
         <xdr:cNvPr id="56" name="image55.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008B010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000038000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4618,7 +4621,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4668,7 +4671,7 @@
         <xdr:cNvPr id="57" name="image56.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008C010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000039000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4718,7 +4721,7 @@
         <xdr:cNvPr id="58" name="image57.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008D010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4768,7 +4771,7 @@
         <xdr:cNvPr id="59" name="image58.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008E010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4818,7 +4821,7 @@
         <xdr:cNvPr id="60" name="image59.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00008F010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00003C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4868,7 +4871,7 @@
         <xdr:cNvPr id="66" name="image56.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000096010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000042000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4918,7 +4921,7 @@
         <xdr:cNvPr id="67" name="image56.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000097010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000043000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4973,7 +4976,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5023,7 +5026,7 @@
         <xdr:cNvPr id="61" name="image60.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000090010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5073,7 +5076,7 @@
         <xdr:cNvPr id="62" name="image61.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000091010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5123,7 +5126,7 @@
         <xdr:cNvPr id="63" name="image62.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000092010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00003F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5173,7 +5176,7 @@
         <xdr:cNvPr id="64" name="image63.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000093010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000040000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5223,7 +5226,7 @@
         <xdr:cNvPr id="65" name="image64.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000094010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000041000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5273,7 +5276,7 @@
         <xdr:cNvPr id="68" name="image66.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000098010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000044000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5323,7 +5326,7 @@
         <xdr:cNvPr id="69" name="image67.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000099010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000045000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5373,7 +5376,7 @@
         <xdr:cNvPr id="158" name="image65.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000F2010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00009E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5428,7 +5431,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5478,7 +5481,7 @@
         <xdr:cNvPr id="79" name="image77.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A3010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00004F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5528,7 +5531,7 @@
         <xdr:cNvPr id="80" name="image78.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A4010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000050000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5583,7 +5586,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5633,7 +5636,7 @@
         <xdr:cNvPr id="70" name="image68.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00009A010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000046000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5683,7 +5686,7 @@
         <xdr:cNvPr id="71" name="image69.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00009B010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000047000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5733,7 +5736,7 @@
         <xdr:cNvPr id="72" name="image70.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00009C010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000048000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5783,7 +5786,7 @@
         <xdr:cNvPr id="73" name="image71.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00009D010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000049000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5833,7 +5836,7 @@
         <xdr:cNvPr id="74" name="image72.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00009E010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00004A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5883,7 +5886,7 @@
         <xdr:cNvPr id="75" name="image73.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00009F010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00004B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5933,7 +5936,7 @@
         <xdr:cNvPr id="76" name="image74.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A0010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00004C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5983,7 +5986,7 @@
         <xdr:cNvPr id="77" name="image75.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A1010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00004D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6033,7 +6036,7 @@
         <xdr:cNvPr id="78" name="image76.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A2010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00004E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6083,7 +6086,7 @@
         <xdr:cNvPr id="81" name="image79.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A5010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000051000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6133,7 +6136,7 @@
         <xdr:cNvPr id="82" name="image80.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A6010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000052000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6183,7 +6186,7 @@
         <xdr:cNvPr id="83" name="image81.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A7010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000053000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6233,7 +6236,7 @@
         <xdr:cNvPr id="84" name="image82.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A8010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000054000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6283,7 +6286,7 @@
         <xdr:cNvPr id="85" name="image83.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000A9010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000055000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6333,7 +6336,7 @@
         <xdr:cNvPr id="86" name="image84.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000AA010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000056000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6383,7 +6386,7 @@
         <xdr:cNvPr id="87" name="image85.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000AB010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000057000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6433,7 +6436,7 @@
         <xdr:cNvPr id="88" name="image86.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000AC010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000058000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6483,7 +6486,7 @@
         <xdr:cNvPr id="89" name="image87.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000AD010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000059000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6533,7 +6536,7 @@
         <xdr:cNvPr id="90" name="image88.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000AE010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00005A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6583,7 +6586,7 @@
         <xdr:cNvPr id="91" name="image89.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000AF010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00005B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6638,7 +6641,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6688,7 +6691,7 @@
         <xdr:cNvPr id="95" name="image93.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B3010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00005F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6738,7 +6741,7 @@
         <xdr:cNvPr id="96" name="image94.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B4010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000060000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6788,7 +6791,7 @@
         <xdr:cNvPr id="97" name="image95.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B5010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000061000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6838,7 +6841,7 @@
         <xdr:cNvPr id="98" name="image96.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B6010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000062000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6888,7 +6891,7 @@
         <xdr:cNvPr id="99" name="image97.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B7010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000063000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6938,7 +6941,7 @@
         <xdr:cNvPr id="100" name="image98.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B8010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000064000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6988,7 +6991,7 @@
         <xdr:cNvPr id="101" name="image99.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000B9010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000065000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7038,7 +7041,7 @@
         <xdr:cNvPr id="102" name="image100.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BA010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000066000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7088,7 +7091,7 @@
         <xdr:cNvPr id="103" name="image101.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BB010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000067000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7138,7 +7141,7 @@
         <xdr:cNvPr id="104" name="image102.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BC010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000068000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7188,7 +7191,7 @@
         <xdr:cNvPr id="105" name="image103.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BD010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000069000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7238,7 +7241,7 @@
         <xdr:cNvPr id="109" name="image107.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C1010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00006D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7293,7 +7296,7 @@
         <xdr:cNvPr id="2" name="image1.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7343,7 +7346,7 @@
         <xdr:cNvPr id="110" name="image108.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C2010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00006E000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7393,7 +7396,7 @@
         <xdr:cNvPr id="111" name="image109.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C3010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00006F000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7443,7 +7446,7 @@
         <xdr:cNvPr id="112" name="image110.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C4010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000070000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7493,7 +7496,7 @@
         <xdr:cNvPr id="113" name="image111.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C5010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000071000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7543,7 +7546,7 @@
         <xdr:cNvPr id="114" name="image112.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C6010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000072000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7593,7 +7596,7 @@
         <xdr:cNvPr id="115" name="image113.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C7010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000073000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7643,7 +7646,7 @@
         <xdr:cNvPr id="116" name="image114.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C8010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000074000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7693,7 +7696,7 @@
         <xdr:cNvPr id="117" name="image115.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000C9010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000075000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7743,7 +7746,7 @@
         <xdr:cNvPr id="118" name="image116.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CA010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000076000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7793,7 +7796,7 @@
         <xdr:cNvPr id="119" name="image117.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CB010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000077000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7843,7 +7846,7 @@
         <xdr:cNvPr id="120" name="image118.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CC010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000078000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7893,7 +7896,7 @@
         <xdr:cNvPr id="121" name="image119.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CD010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000079000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7943,7 +7946,7 @@
         <xdr:cNvPr id="122" name="image120.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CE010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007A000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7993,7 +7996,7 @@
         <xdr:cNvPr id="123" name="image121.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000CF010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8043,7 +8046,7 @@
         <xdr:cNvPr id="124" name="image122.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000D0010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8093,7 +8096,7 @@
         <xdr:cNvPr id="125" name="image123.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000D1010000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00007D000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8129,9 +8132,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8169,9 +8172,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8206,7 +8209,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8241,7 +8244,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8414,7 +8417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AT9"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -8437,89 +8440,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -8552,11 +8555,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -8566,8 +8569,8 @@
       <c r="I4" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -8577,10 +8580,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -8611,25 +8614,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -8770,10 +8773,10 @@
       </c>
       <c r="L7" s="8">
         <f t="shared" ref="L7:L9" si="0">M7*(1-0.1)</f>
-        <v>14850</v>
+        <v>13860</v>
       </c>
       <c r="M7" s="14">
-        <v>16500</v>
+        <v>15400</v>
       </c>
       <c r="N7" s="7">
         <v>0.1</v>
@@ -8981,12 +8984,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -8997,6 +8994,12 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -9005,7 +9008,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:AT8"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -9028,89 +9031,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -9143,11 +9146,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -9157,8 +9160,8 @@
       <c r="I4" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -9168,10 +9171,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -9202,25 +9205,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -9441,10 +9444,10 @@
       </c>
       <c r="L8" s="8">
         <f t="shared" si="0"/>
-        <v>6525</v>
+        <v>4815</v>
       </c>
       <c r="M8" s="14">
-        <v>7250</v>
+        <v>5350</v>
       </c>
       <c r="N8" s="7">
         <v>0.1</v>
@@ -9492,12 +9495,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -9508,6 +9505,12 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -9516,7 +9519,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:AT11"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -9539,89 +9542,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -9654,11 +9657,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -9668,8 +9671,8 @@
       <c r="I4" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -9679,10 +9682,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -9713,25 +9716,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -10159,12 +10162,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -10175,6 +10172,12 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -10183,7 +10186,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:AT21"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -10206,89 +10209,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -10321,11 +10324,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -10333,8 +10336,8 @@
       <c r="I4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -10344,10 +10347,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -10378,41 +10381,41 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B6" s="32">
+      <c r="B6" s="36">
         <v>61</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="41" t="s">
         <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="28"/>
-      <c r="F6" s="24" t="s">
+      <c r="E6" s="46"/>
+      <c r="F6" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="19" t="s">
@@ -10421,7 +10424,7 @@
       <c r="I6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="J6" s="44" t="s">
         <v>49</v>
       </c>
       <c r="K6" s="4" t="s">
@@ -10449,21 +10452,21 @@
       </c>
     </row>
     <row r="7" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B7" s="33"/>
-      <c r="C7" s="25"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="25"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="42"/>
       <c r="H7" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="26"/>
+      <c r="J7" s="43"/>
       <c r="K7" s="4" t="s">
         <v>199</v>
       </c>
@@ -10489,20 +10492,20 @@
       </c>
     </row>
     <row r="8" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B8" s="32">
+      <c r="B8" s="36">
         <v>62</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="41" t="s">
         <v>40</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="24" t="s">
+      <c r="E8" s="46"/>
+      <c r="F8" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="19" t="s">
@@ -10511,7 +10514,7 @@
       <c r="I8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="45" t="s">
+      <c r="J8" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K8" s="4" t="s">
@@ -10541,21 +10544,21 @@
       </c>
     </row>
     <row r="9" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B9" s="33"/>
-      <c r="C9" s="25"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="42"/>
       <c r="D9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="25"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="43"/>
       <c r="K9" s="4" t="s">
         <v>199</v>
       </c>
@@ -10583,20 +10586,20 @@
       </c>
     </row>
     <row r="10" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B10" s="32">
+      <c r="B10" s="36">
         <v>65</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="41" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="28"/>
-      <c r="F10" s="24" t="s">
+      <c r="E10" s="46"/>
+      <c r="F10" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="19" t="s">
@@ -10605,7 +10608,7 @@
       <c r="I10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="45" t="s">
+      <c r="J10" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K10" s="4" t="s">
@@ -10635,21 +10638,21 @@
       </c>
     </row>
     <row r="11" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B11" s="33"/>
-      <c r="C11" s="25"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="42"/>
       <c r="D11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="25"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="43"/>
       <c r="K11" s="4" t="s">
         <v>199</v>
       </c>
@@ -10677,20 +10680,20 @@
       </c>
     </row>
     <row r="12" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B12" s="32">
+      <c r="B12" s="36">
         <v>66</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="41" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="24" t="s">
+      <c r="E12" s="39"/>
+      <c r="F12" s="41" t="s">
         <v>158</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="19" t="s">
@@ -10699,7 +10702,7 @@
       <c r="I12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="45" t="s">
+      <c r="J12" s="44" t="s">
         <v>49</v>
       </c>
       <c r="K12" s="4" t="s">
@@ -10727,21 +10730,21 @@
       </c>
     </row>
     <row r="13" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B13" s="33"/>
-      <c r="C13" s="25"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="42"/>
       <c r="D13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="25"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J13" s="26"/>
+      <c r="J13" s="43"/>
       <c r="K13" s="4" t="s">
         <v>199</v>
       </c>
@@ -10767,20 +10770,20 @@
       </c>
     </row>
     <row r="14" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B14" s="32">
+      <c r="B14" s="36">
         <v>67</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="24" t="s">
+      <c r="E14" s="39"/>
+      <c r="F14" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="19" t="s">
@@ -10789,7 +10792,7 @@
       <c r="I14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="45" t="s">
+      <c r="J14" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K14" s="4" t="s">
@@ -10819,21 +10822,21 @@
       </c>
     </row>
     <row r="15" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B15" s="33"/>
-      <c r="C15" s="25"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="42"/>
       <c r="D15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="25"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="42"/>
       <c r="H15" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="26"/>
+      <c r="J15" s="43"/>
       <c r="K15" s="4" t="s">
         <v>199</v>
       </c>
@@ -10861,20 +10864,20 @@
       </c>
     </row>
     <row r="16" spans="2:46" ht="80.099999999999994" customHeight="1">
-      <c r="B16" s="32">
+      <c r="B16" s="36">
         <v>68</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="41" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="24" t="s">
+      <c r="E16" s="39"/>
+      <c r="F16" s="41" t="s">
         <v>156</v>
       </c>
-      <c r="G16" s="24" t="s">
+      <c r="G16" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="19" t="s">
@@ -10883,7 +10886,7 @@
       <c r="I16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="45" t="s">
+      <c r="J16" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K16" s="4" t="s">
@@ -10891,10 +10894,10 @@
       </c>
       <c r="L16" s="8">
         <f t="shared" si="0"/>
-        <v>15480</v>
+        <v>13050</v>
       </c>
       <c r="M16" s="6">
-        <v>17200</v>
+        <v>14500</v>
       </c>
       <c r="N16" s="7">
         <v>0.1</v>
@@ -10913,21 +10916,21 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B17" s="33"/>
-      <c r="C17" s="27"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="45"/>
       <c r="D17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="25"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="42"/>
       <c r="H17" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="43"/>
       <c r="K17" s="4" t="s">
         <v>199</v>
       </c>
@@ -10955,20 +10958,20 @@
       </c>
     </row>
     <row r="18" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B18" s="32">
+      <c r="B18" s="36">
         <v>69</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="38" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="24" t="s">
+      <c r="E18" s="39"/>
+      <c r="F18" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="19" t="s">
@@ -10977,7 +10980,7 @@
       <c r="I18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J18" s="45" t="s">
+      <c r="J18" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K18" s="4" t="s">
@@ -10985,10 +10988,10 @@
       </c>
       <c r="L18" s="8">
         <f t="shared" si="0"/>
-        <v>18450</v>
+        <v>17550</v>
       </c>
       <c r="M18" s="6">
-        <v>20500</v>
+        <v>19500</v>
       </c>
       <c r="N18" s="7">
         <v>0.1</v>
@@ -11007,21 +11010,21 @@
       </c>
     </row>
     <row r="19" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B19" s="33"/>
-      <c r="C19" s="46"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="25"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="42"/>
       <c r="H19" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J19" s="26"/>
+      <c r="J19" s="43"/>
       <c r="K19" s="4" t="s">
         <v>199</v>
       </c>
@@ -11049,18 +11052,18 @@
       </c>
     </row>
     <row r="20" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B20" s="32">
+      <c r="B20" s="36">
         <v>70</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="38" t="s">
         <v>46</v>
       </c>
       <c r="D20" s="15"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="24" t="s">
+      <c r="E20" s="39"/>
+      <c r="F20" s="41" t="s">
         <v>154</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="41" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="19" t="s">
@@ -11069,7 +11072,7 @@
       <c r="I20" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="41" t="s">
         <v>51</v>
       </c>
       <c r="K20" s="4" t="s">
@@ -11077,9 +11080,11 @@
       </c>
       <c r="L20" s="8">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="5"/>
+        <v>67500</v>
+      </c>
+      <c r="M20" s="5">
+        <v>75000</v>
+      </c>
       <c r="N20" s="7">
         <v>0.1</v>
       </c>
@@ -11097,21 +11102,21 @@
       </c>
     </row>
     <row r="21" spans="2:18" ht="80.099999999999994" customHeight="1">
-      <c r="B21" s="33"/>
-      <c r="C21" s="46"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="38"/>
       <c r="D21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
       <c r="H21" s="19" t="s">
         <v>38</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J21" s="25"/>
+      <c r="J21" s="42"/>
       <c r="K21" s="4" t="s">
         <v>199</v>
       </c>
@@ -11138,60 +11143,6 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="J20:J21"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="F18:F19"/>
-    <mergeCell ref="G18:G19"/>
-    <mergeCell ref="J18:J19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="J12:J13"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -11202,6 +11153,60 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="J20:J21"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="F18:F19"/>
+    <mergeCell ref="G18:G19"/>
+    <mergeCell ref="J18:J19"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="G20:G21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -11210,7 +11215,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AT7"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -11233,89 +11238,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -11348,11 +11353,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -11360,8 +11365,8 @@
       <c r="I4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -11371,10 +11376,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -11405,25 +11410,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:46" ht="80.099999999999994" customHeight="1">
       <c r="B6" s="3">
@@ -11435,7 +11440,7 @@
       <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="39"/>
       <c r="F6" s="4" t="s">
         <v>347</v>
       </c>
@@ -11456,9 +11461,11 @@
       </c>
       <c r="L6" s="8">
         <f>M6*(1-0.1)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="12"/>
+        <v>34920</v>
+      </c>
+      <c r="M6" s="12">
+        <v>38800</v>
+      </c>
       <c r="N6" s="7">
         <v>0.1</v>
       </c>
@@ -11485,7 +11492,7 @@
       <c r="D7" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="E7" s="31"/>
+      <c r="E7" s="40"/>
       <c r="F7" s="4" t="s">
         <v>342</v>
       </c>
@@ -11506,9 +11513,11 @@
       </c>
       <c r="L7" s="8">
         <f>M7*(1-0.1)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="12"/>
+        <v>35100</v>
+      </c>
+      <c r="M7" s="12">
+        <v>39000</v>
+      </c>
       <c r="N7" s="7">
         <v>0.1</v>
       </c>
@@ -11527,13 +11536,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -11544,6 +11546,13 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -11552,7 +11561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:AT25"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -11575,89 +11584,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -11690,11 +11699,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -11702,8 +11711,8 @@
       <c r="I4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -11713,10 +11722,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -11747,25 +11756,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:46" ht="80.099999999999994" customHeight="1">
       <c r="B6" s="3">
@@ -11954,10 +11963,10 @@
       </c>
       <c r="L9" s="8">
         <f t="shared" si="0"/>
-        <v>2880</v>
+        <v>28800</v>
       </c>
       <c r="M9" s="5">
-        <v>3200</v>
+        <v>32000</v>
       </c>
       <c r="N9" s="7">
         <v>0.1</v>
@@ -12809,12 +12818,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -12825,6 +12828,12 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -12833,7 +12842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:AT17"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -12856,89 +12865,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -12971,11 +12980,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -12985,8 +12994,8 @@
       <c r="I4" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -12996,10 +13005,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -13030,25 +13039,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:46" ht="90" customHeight="1">
       <c r="B6" s="3">
@@ -13083,7 +13092,7 @@
         <f>M6*(1-0.1)</f>
         <v>23400</v>
       </c>
-      <c r="M6" s="47">
+      <c r="M6" s="21">
         <v>26000</v>
       </c>
       <c r="N6" s="7">
@@ -13135,7 +13144,7 @@
         <f t="shared" ref="L7:L17" si="0">M7*(1-0.1)</f>
         <v>23400</v>
       </c>
-      <c r="M7" s="47">
+      <c r="M7" s="21">
         <v>26000</v>
       </c>
       <c r="N7" s="7">
@@ -13187,7 +13196,7 @@
         <f t="shared" si="0"/>
         <v>23400</v>
       </c>
-      <c r="M8" s="47">
+      <c r="M8" s="21">
         <v>26000</v>
       </c>
       <c r="N8" s="7">
@@ -13239,7 +13248,7 @@
         <f t="shared" si="0"/>
         <v>21600</v>
       </c>
-      <c r="M9" s="47">
+      <c r="M9" s="21">
         <v>24000</v>
       </c>
       <c r="N9" s="7">
@@ -13291,7 +13300,7 @@
         <f t="shared" si="0"/>
         <v>7110</v>
       </c>
-      <c r="M10" s="47">
+      <c r="M10" s="21">
         <v>7900</v>
       </c>
       <c r="N10" s="7">
@@ -13343,7 +13352,7 @@
         <f t="shared" si="0"/>
         <v>7200</v>
       </c>
-      <c r="M11" s="47">
+      <c r="M11" s="21">
         <v>8000</v>
       </c>
       <c r="N11" s="7">
@@ -13393,10 +13402,10 @@
       </c>
       <c r="L12" s="8">
         <f t="shared" si="0"/>
-        <v>6318</v>
-      </c>
-      <c r="M12" s="47">
-        <v>7020</v>
+        <v>8100</v>
+      </c>
+      <c r="M12" s="21">
+        <v>9000</v>
       </c>
       <c r="N12" s="7">
         <v>0.1</v>
@@ -13445,10 +13454,10 @@
       </c>
       <c r="L13" s="8">
         <f t="shared" si="0"/>
-        <v>18252</v>
-      </c>
-      <c r="M13" s="47">
-        <v>20280</v>
+        <v>23400</v>
+      </c>
+      <c r="M13" s="21">
+        <v>26000</v>
       </c>
       <c r="N13" s="7">
         <v>0.1</v>
@@ -13655,7 +13664,7 @@
         <f t="shared" si="0"/>
         <v>11700</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M17" s="21">
         <v>13000</v>
       </c>
       <c r="N17" s="7">
@@ -13676,12 +13685,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -13692,6 +13695,12 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
@@ -13700,7 +13709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:AT21"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -13723,89 +13732,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="35"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="29"/>
     </row>
     <row r="2" spans="2:46" ht="39.950000000000003" customHeight="1">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="37"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="31"/>
     </row>
     <row r="3" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="40" t="s">
+      <c r="L3" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="40"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="44" t="s">
+      <c r="M3" s="25"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="40" t="s">
+      <c r="P3" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="40" t="s">
+      <c r="Q3" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="40" t="s">
+      <c r="R3" s="25" t="s">
         <v>168</v>
       </c>
       <c r="S3" s="2"/>
@@ -13838,11 +13847,11 @@
       <c r="AT3" s="2"/>
     </row>
     <row r="4" spans="2:46" ht="33.200000000000003" customHeight="1">
-      <c r="B4" s="39"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="20" t="s">
         <v>17</v>
       </c>
@@ -13852,8 +13861,8 @@
       <c r="I4" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="J4" s="40"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="35"/>
       <c r="L4" s="1" t="s">
         <v>9</v>
       </c>
@@ -13863,10 +13872,10 @@
       <c r="N4" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -13897,25 +13906,25 @@
       <c r="AT4" s="2"/>
     </row>
     <row r="5" spans="2:46" ht="50.1" customHeight="1">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="24"/>
     </row>
     <row r="6" spans="2:46" ht="80.099999999999994" customHeight="1">
       <c r="B6" s="3">
@@ -14104,10 +14113,10 @@
       </c>
       <c r="L9" s="8">
         <f t="shared" si="0"/>
-        <v>5580</v>
+        <v>5220</v>
       </c>
       <c r="M9" s="14">
-        <v>6200</v>
+        <v>5800</v>
       </c>
       <c r="N9" s="7">
         <v>0.1</v>
@@ -14156,10 +14165,10 @@
       </c>
       <c r="L10" s="8">
         <f t="shared" si="0"/>
-        <v>4950</v>
+        <v>4050</v>
       </c>
       <c r="M10" s="14">
-        <v>5500</v>
+        <v>4500</v>
       </c>
       <c r="N10" s="7">
         <v>0.1</v>
@@ -14208,10 +14217,10 @@
       </c>
       <c r="L11" s="8">
         <f t="shared" si="0"/>
-        <v>4140</v>
+        <v>3420</v>
       </c>
       <c r="M11" s="14">
-        <v>4600</v>
+        <v>3800</v>
       </c>
       <c r="N11" s="7">
         <v>0.1</v>
@@ -14364,10 +14373,10 @@
       </c>
       <c r="L14" s="8">
         <f t="shared" si="0"/>
-        <v>7200</v>
+        <v>5760</v>
       </c>
       <c r="M14" s="14">
-        <v>8000</v>
+        <v>6400</v>
       </c>
       <c r="N14" s="7">
         <v>0.1</v>
@@ -14416,10 +14425,10 @@
       </c>
       <c r="L15" s="8">
         <f t="shared" si="0"/>
-        <v>2835</v>
+        <v>3330</v>
       </c>
       <c r="M15" s="14">
-        <v>3150</v>
+        <v>3700</v>
       </c>
       <c r="N15" s="7">
         <v>0.1</v>
@@ -14468,10 +14477,10 @@
       </c>
       <c r="L16" s="8">
         <f t="shared" si="0"/>
-        <v>2655</v>
+        <v>2520</v>
       </c>
       <c r="M16" s="14">
-        <v>2950</v>
+        <v>2800</v>
       </c>
       <c r="N16" s="7">
         <v>0.1</v>
@@ -14520,10 +14529,10 @@
       </c>
       <c r="L17" s="8">
         <f t="shared" si="0"/>
-        <v>4140</v>
+        <v>3960</v>
       </c>
       <c r="M17" s="14">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="N17" s="7">
         <v>0.1</v>
@@ -14572,10 +14581,10 @@
       </c>
       <c r="L18" s="8">
         <f t="shared" si="0"/>
-        <v>6300</v>
+        <v>9450</v>
       </c>
       <c r="M18" s="14">
-        <v>7000</v>
+        <v>10500</v>
       </c>
       <c r="N18" s="7">
         <v>0.1</v>
@@ -14626,7 +14635,7 @@
         <f t="shared" si="0"/>
         <v>10620</v>
       </c>
-      <c r="M19" s="47">
+      <c r="M19" s="21">
         <v>11800</v>
       </c>
       <c r="N19" s="7">
@@ -14676,10 +14685,10 @@
       </c>
       <c r="L20" s="8">
         <f t="shared" si="0"/>
-        <v>5850</v>
+        <v>5130</v>
       </c>
       <c r="M20" s="14">
-        <v>6500</v>
+        <v>5700</v>
       </c>
       <c r="N20" s="7">
         <v>0.1</v>
@@ -14751,12 +14760,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B5:R5"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="R3:R4"/>
     <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="B3:B4"/>
@@ -14767,6 +14770,12 @@
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="B5:R5"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="10" orientation="portrait" r:id="rId1"/>
